--- a/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB72D190-63F1-422B-9175-63154ED10821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A643A745-807C-4E58-B7BD-2DCEFEA53E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A643A745-807C-4E58-B7BD-2DCEFEA53E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48F6D470-7FED-4BAF-BDD5-CC53FBB68723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
